--- a/data/trans_dic/IP31KM08_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM08_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,1; 53,63</t>
+          <t>36,7; 52,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,15; 56,5</t>
+          <t>35,38; 51,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,52; 51,95</t>
+          <t>38,34; 50,29</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,02; 49,99</t>
+          <t>44,75; 62,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,54; 61,07</t>
+          <t>34,05; 51,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,17; 53,03</t>
+          <t>41,66; 54,41</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>55,56%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,61; 67,28</t>
+          <t>40,02; 63,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,54; 61,59</t>
+          <t>45,48; 70,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,74; 61,19</t>
+          <t>47,23; 63,87</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,57; 39,55</t>
+          <t>35,68; 49,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,33; 47,61</t>
+          <t>30,29; 42,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,07; 41,4</t>
+          <t>35,32; 44,57</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,06; 62,4</t>
+          <t>32,47; 49,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,75; 48,38</t>
+          <t>49,77; 64,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,67; 52,27</t>
+          <t>42,09; 54,49</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42,71; 63,51</t>
+          <t>35,71; 58,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,56; 57,63</t>
+          <t>44,21; 65,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,33; 57,79</t>
+          <t>43,68; 59,05</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,01; 47,42</t>
+          <t>42,03; 48,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,72; 48,25</t>
+          <t>43,29; 50,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,8; 47,0</t>
+          <t>43,43; 48,67</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44857</t>
+          <t>53891</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63493</t>
+          <t>43686</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108350</t>
+          <t>97577</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36718; 54551</t>
+          <t>44481; 63591</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52927; 76379</t>
+          <t>35506; 51938</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93608; 123072</t>
+          <t>84953; 111428</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>38756</t>
+          <t>48193</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49166</t>
+          <t>40717</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87923</t>
+          <t>88910</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30837; 46688</t>
+          <t>40224; 56577</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39864; 57229</t>
+          <t>32483; 48911</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75160; 99215</t>
+          <t>77193; 100810</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28041</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58742</t>
+          <t>59919</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21344; 33700</t>
+          <t>22350; 35604</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23399; 38391</t>
+          <t>23653; 36591</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49174; 68787</t>
+          <t>50942; 68891</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>99</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>68414</t>
+          <t>84106</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>87016</t>
+          <t>64606</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155430</t>
+          <t>148712</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46484; 85237</t>
+          <t>70400; 97517</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73011; 101256</t>
+          <t>53511; 75512</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124494; 177260</t>
+          <t>132083; 166675</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62944</t>
+          <t>61305</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64710</t>
+          <t>66426</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127654</t>
+          <t>127731</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>53204; 72077</t>
+          <t>47268; 72223</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49027; 77149</t>
+          <t>57470; 74909</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106338; 143720</t>
+          <t>109878; 142247</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>37029</t>
+          <t>31167</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32224</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69252</t>
+          <t>70032</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29422; 43757</t>
+          <t>23517; 38409</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24546; 39783</t>
+          <t>31107; 46027</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58380; 79709</t>
+          <t>59500; 80436</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>403</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>280041</t>
+          <t>308079</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>327310</t>
+          <t>284802</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>607352</t>
+          <t>592881</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>238736; 305898</t>
+          <t>283971; 329881</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>298254; 353363</t>
+          <t>264178; 305471</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>561957; 647430</t>
+          <t>558430; 625848</t>
         </is>
       </c>
     </row>
